--- a/data/raw/legal_corpus/manifest/tax/document_manifest.xlsx
+++ b/data/raw/legal_corpus/manifest/tax/document_manifest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,7 +538,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DOC_01</t>
+          <t>DOC_TAX_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DOC_02</t>
+          <t>DOC_TAX_02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -720,7 +720,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DOC_03</t>
+          <t>DOC_TAX_03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DOC_04</t>
+          <t>DOC_TAX_04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -902,7 +902,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DOC_05</t>
+          <t>DOC_TAX_05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DOC_06</t>
+          <t>DOC_TAX_06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1080,7 +1080,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DOC_07</t>
+          <t>DOC_TAX_07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1167,6 +1167,350 @@
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DOC_TAX_08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>70/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>08 70 2025 ND-CP 577816</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Chính phủ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ngày 20 tháng 3 năm 2025</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>08_70_2025_ND-CP_577816.doc</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>doc</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>doanh_nghiep</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>van_ban_khac</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>uu_tien_nghia_vu_quyen_dieu_kien</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>cao</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DOC_TAX_09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>123/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>09 32 2025 TT-BTC 659105</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Chính phủ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ngày 31 tháng 5 năm 2025</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>09_32_2025_TT-BTC_659105.doc</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>doc</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>doanh_nghiep</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>van_ban_khac</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>uu_tien_nghia_vu_quyen_dieu_kien</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>cao</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DOC_TAX_10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>181/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10 69 2025 TT-BTC 663356</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Chính phủ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ngày 01 tháng 7 năm 2025</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>10_69_2025_TT-BTC_663356.doc</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>doc</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>doanh_nghiep</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>van_ban_khac</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>uu_tien_nghia_vu_quyen_dieu_kien</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>cao</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DOC_TAX_11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 71_2014_QH13_259208</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>11  71 2014 QH13 259208</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ngày 26 tháng 11 năm 2014</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>11_ 71_2014_QH13_259208.doc</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>doc</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>doanh_nghiep</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>van_ban_khac</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>trung_binh</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>uu_tien_nghia_vu_quyen_dieu_kien</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>cao</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
